--- a/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,4</t>
+          <t>-1,53; 4,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,77</t>
+          <t>-2,22; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,25</t>
+          <t>2,81; 8,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,99</t>
+          <t>-0,79; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,53</t>
+          <t>-1,92; 4,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,08</t>
+          <t>-0,19; 5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,31</t>
+          <t>-0,25; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,93</t>
+          <t>-1,35; 2,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,4</t>
+          <t>2,14; 6,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 215,61</t>
+          <t>-39,07; 182,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 130,88</t>
+          <t>-50,8; 125,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,53; 437,3</t>
+          <t>47,68; 437,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 277,27</t>
+          <t>-23,53; 293,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 232,45</t>
+          <t>-40,95; 200,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 256,51</t>
+          <t>-9,68; 275,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 182,37</t>
+          <t>-8,53; 169,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 119,82</t>
+          <t>-32,11; 107,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,24; 266,85</t>
+          <t>42,04; 249,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,7</t>
+          <t>-0,07; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,77</t>
+          <t>-0,99; 4,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,54</t>
+          <t>1,23; 7,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,26</t>
+          <t>-1,66; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,78</t>
+          <t>-3,95; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,0</t>
+          <t>-1,06; 4,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,37</t>
+          <t>-0,14; 4,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,51</t>
+          <t>-1,72; 2,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,49</t>
+          <t>1,09; 5,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 384,67</t>
+          <t>-13,66; 396,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 286,81</t>
+          <t>-30,58; 309,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 549,63</t>
+          <t>21,05; 559,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 177,45</t>
+          <t>-28,29; 181,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 58,56</t>
+          <t>-67,78; 80,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 188,51</t>
+          <t>-17,87; 168,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 154,97</t>
+          <t>-4,32; 159,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 103,83</t>
+          <t>-39,86; 100,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,77; 222,5</t>
+          <t>20,5; 207,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,35</t>
+          <t>-0,46; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,45</t>
+          <t>-2,5; 3,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,88</t>
+          <t>-4,56; 8,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 5,81</t>
+          <t>-5,08; 6,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 6,07</t>
+          <t>-5,95; 6,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 10,38</t>
+          <t>-2,44; 9,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,73</t>
+          <t>-0,46; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,15</t>
+          <t>-2,28; 3,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 6,89</t>
+          <t>-3,58; 6,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 117,48</t>
+          <t>-8,28; 126,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 73,0</t>
+          <t>-35,25; 76,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 139,5</t>
+          <t>-56,84; 152,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 108,65</t>
+          <t>-45,85; 123,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 114,07</t>
+          <t>-56,38; 135,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 205,2</t>
+          <t>-23,47; 196,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 95,66</t>
+          <t>-8,26; 98,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 59,44</t>
+          <t>-30,09; 71,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 116,42</t>
+          <t>-45,23; 115,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,25</t>
+          <t>0,62; 5,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,24</t>
+          <t>-1,84; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,79</t>
+          <t>3,86; 8,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,97</t>
+          <t>0,11; 5,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,21</t>
+          <t>-2,6; 2,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 56,27</t>
+          <t>1,55; 50,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,78</t>
+          <t>1,27; 4,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,89</t>
+          <t>-1,26; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 36,02</t>
+          <t>4,07; 40,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 94,55</t>
+          <t>7,93; 95,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 42,35</t>
+          <t>-25,87; 41,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,61; 164,13</t>
+          <t>54,17; 165,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 115,77</t>
+          <t>1,53; 117,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 63,14</t>
+          <t>-31,99; 54,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,25; 1063,79</t>
+          <t>21,94; 947,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,04; 85,01</t>
+          <t>17,75; 85,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 33,42</t>
+          <t>-17,65; 32,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,63; 573,74</t>
+          <t>61,64; 677,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,62</t>
+          <t>-3,21; 3,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 2,11</t>
+          <t>-4,17; 2,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,4</t>
+          <t>6,52; 15,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,28</t>
+          <t>0,59; 7,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,86</t>
+          <t>-2,58; 3,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,51</t>
+          <t>1,1; 8,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,94</t>
+          <t>0,22; 4,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,11</t>
+          <t>-2,35; 2,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,32</t>
+          <t>4,32; 10,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 84,27</t>
+          <t>-38,01; 94,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 47,09</t>
+          <t>-47,23; 57,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67,44; 346,15</t>
+          <t>78,69; 367,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,93; 129,79</t>
+          <t>4,68; 119,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 68,44</t>
+          <t>-27,79; 60,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,07; 144,13</t>
+          <t>14,18; 152,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 88,28</t>
+          <t>2,64; 85,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 39,28</t>
+          <t>-28,89; 35,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>55,44; 175,84</t>
+          <t>54,76; 171,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,92</t>
+          <t>-0,48; 6,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 6,16</t>
+          <t>-0,2; 6,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,77</t>
+          <t>-0,49; 7,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,85</t>
+          <t>0,41; 5,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,34</t>
+          <t>-0,84; 3,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,59</t>
+          <t>6,3; 11,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,63</t>
+          <t>0,69; 4,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,57</t>
+          <t>-0,27; 3,46</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,56</t>
+          <t>4,93; 9,65</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 500,08</t>
+          <t>-30,18; 611,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 542,97</t>
+          <t>-17,74; 699,75</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 742,96</t>
+          <t>-42,61; 746,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,44; 87,48</t>
+          <t>5,33; 92,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 59,66</t>
+          <t>-11,61; 62,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,87; 203,59</t>
+          <t>82,11; 209,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,53; 93,43</t>
+          <t>10,56; 95,48</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 72,68</t>
+          <t>-4,49; 70,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>78,72; 192,96</t>
+          <t>73,71; 203,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,49</t>
+          <t>1,26; 3,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,77</t>
+          <t>-0,51; 1,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,1</t>
+          <t>2,89; 6,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,15</t>
+          <t>1,57; 4,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,88</t>
+          <t>-0,56; 1,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,22; 26,17</t>
+          <t>4,21; 25,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,48</t>
+          <t>1,73; 3,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,44</t>
+          <t>-0,19; 1,42</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,54</t>
+          <t>4,68; 16,97</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>20,47; 80,27</t>
+          <t>23,01; 79,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 39,66</t>
+          <t>-9,28; 36,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56,74; 154,22</t>
+          <t>57,99; 153,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,66; 74,3</t>
+          <t>23,91; 75,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 33,28</t>
+          <t>-8,36; 33,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>66,6; 450,21</t>
+          <t>64,2; 421,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,44; 66,0</t>
+          <t>28,61; 65,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 27,85</t>
+          <t>-3,25; 27,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>80,72; 307,87</t>
+          <t>80,26; 301,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,46</t>
+          <t>-1,45; 4,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,8</t>
+          <t>-2,2; 2,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,94</t>
+          <t>2,61; 8,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,04</t>
+          <t>-1,14; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,09</t>
+          <t>-2,07; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,18</t>
+          <t>-0,38; 5,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,16</t>
+          <t>-0,38; 4,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,64</t>
+          <t>-1,24; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,27</t>
+          <t>1,77; 5,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171,95%</t>
+          <t>159,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125,36%</t>
+          <t>118,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 182,72</t>
+          <t>-37,3; 188,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 125,05</t>
+          <t>-49,45; 144,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,68; 437,16</t>
+          <t>51,12; 381,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 293,33</t>
+          <t>-28,09; 294,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 200,05</t>
+          <t>-43,89; 237,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 275,72</t>
+          <t>-9,18; 311,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 169,22</t>
+          <t>-12,45; 162,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 107,83</t>
+          <t>-30,08; 123,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,04; 249,77</t>
+          <t>36,92; 245,92</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,84</t>
+          <t>-0,1; 5,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,5</t>
+          <t>-0,88; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,37</t>
+          <t>1,34; 7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,32</t>
+          <t>-1,76; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,88</t>
+          <t>-4,45; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,91</t>
+          <t>-1,04; 5,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,31</t>
+          <t>-0,2; 4,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,36</t>
+          <t>-1,91; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,38</t>
+          <t>1,11; 5,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160,27%</t>
+          <t>157,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 396,11</t>
+          <t>-11,18; 363,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 309,02</t>
+          <t>-28,15; 296,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 559,7</t>
+          <t>16,93; 480,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 181,67</t>
+          <t>-34,43; 186,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 80,62</t>
+          <t>-73,54; 55,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 168,88</t>
+          <t>-16,24; 213,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 159,07</t>
+          <t>-9,37; 167,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 100,32</t>
+          <t>-40,46; 96,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 207,55</t>
+          <t>20,49; 213,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>5,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,72</t>
+          <t>-0,56; 5,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,45</t>
+          <t>-2,09; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 8,1</t>
+          <t>2,79; 9,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 6,25</t>
+          <t>-4,66; 6,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,91</t>
+          <t>-5,99; 6,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 9,86</t>
+          <t>-1,87; 10,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,04</t>
+          <t>-0,52; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,34</t>
+          <t>-2,27; 3,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,89</t>
+          <t>2,65; 9,07</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>105,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 126,43</t>
+          <t>-7,55; 128,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 76,17</t>
+          <t>-30,8; 79,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 152,42</t>
+          <t>33,46; 212,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 123,77</t>
+          <t>-42,09; 127,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 135,0</t>
+          <t>-55,54; 123,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 196,94</t>
+          <t>-19,79; 221,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 98,34</t>
+          <t>-7,08; 100,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 71,11</t>
+          <t>-29,8; 67,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 115,97</t>
+          <t>32,64; 178,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,38</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>4,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,08</t>
+          <t>0,68; 5,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,16</t>
+          <t>-1,9; 2,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,77</t>
+          <t>3,84; 8,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,93</t>
+          <t>0,2; 6,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,82</t>
+          <t>-2,37; 3,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 50,18</t>
+          <t>-0,13; 4,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,76</t>
+          <t>1,28; 4,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,79</t>
+          <t>-1,37; 1,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 40,97</t>
+          <t>2,76; 6,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323,15%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212,85%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 95,11</t>
+          <t>9,33; 101,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 41,19</t>
+          <t>-27,04; 38,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,17; 165,98</t>
+          <t>51,25; 159,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 117,0</t>
+          <t>1,29; 124,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 54,83</t>
+          <t>-29,3; 59,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,94; 947,86</t>
+          <t>-2,11; 94,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 85,87</t>
+          <t>16,64; 87,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 32,53</t>
+          <t>-18,35; 33,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,64; 677,84</t>
+          <t>37,47; 111,04</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,98</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>7,6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,52</t>
+          <t>8,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,89</t>
+          <t>-3,19; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,45</t>
+          <t>-4,46; 2,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 15,59</t>
+          <t>4,49; 13,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,02</t>
+          <t>0,27; 6,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,46</t>
+          <t>-2,64; 3,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,8</t>
+          <t>4,5; 10,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,87</t>
+          <t>-0,25; 4,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,0</t>
+          <t>-2,47; 2,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,02</t>
+          <t>5,48; 10,33</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173,69%</t>
+          <t>138,64%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>102,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>107,16%</t>
+          <t>114,63%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 94,55</t>
+          <t>-39,75; 89,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 57,3</t>
+          <t>-49,89; 56,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78,69; 367,17</t>
+          <t>46,89; 288,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,68; 119,31</t>
+          <t>3,52; 117,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 60,08</t>
+          <t>-28,84; 56,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,18; 152,74</t>
+          <t>43,92; 181,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,64; 85,79</t>
+          <t>-2,9; 80,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 35,05</t>
+          <t>-29,76; 37,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54,76; 171,76</t>
+          <t>66,36; 186,0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 6,39</t>
+          <t>-0,38; 6,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,31</t>
+          <t>-0,05; 5,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,96</t>
+          <t>-0,53; 8,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,09</t>
+          <t>0,61; 4,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,51</t>
+          <t>-0,73; 3,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,36</t>
+          <t>5,94; 11,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,55</t>
+          <t>0,71; 4,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,46</t>
+          <t>-0,39; 3,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,65</t>
+          <t>5,07; 9,51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130,84%</t>
+          <t>132,8%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>136,9%</t>
+          <t>130,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>127,75%</t>
+          <t>125,98%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 611,17</t>
+          <t>-30,41; 596,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 699,75</t>
+          <t>-14,45; 545,29</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 746,38</t>
+          <t>-34,35; 762,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,33; 92,13</t>
+          <t>7,65; 90,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 62,17</t>
+          <t>-10,43; 60,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>82,11; 209,36</t>
+          <t>80,83; 208,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,56; 95,48</t>
+          <t>9,75; 91,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 70,77</t>
+          <t>-6,75; 71,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73,71; 203,35</t>
+          <t>77,47; 194,14</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>5,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,63</t>
+          <t>1,1; 3,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,65</t>
+          <t>-0,4; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,97</t>
+          <t>4,56; 7,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,15</t>
+          <t>1,61; 4,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,97</t>
+          <t>-0,72; 1,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,21; 25,63</t>
+          <t>3,84; 6,31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,48</t>
+          <t>1,7; 3,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,42</t>
+          <t>-0,27; 1,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,97</t>
+          <t>4,59; 6,4</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109,24%</t>
+          <t>117,52%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>155,22%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>135,79%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,01; 79,81</t>
+          <t>19,84; 78,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 36,47</t>
+          <t>-7,32; 40,69</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57,99; 153,83</t>
+          <t>82,77; 160,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23,91; 75,67</t>
+          <t>22,71; 76,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 33,78</t>
+          <t>-10,14; 32,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,2; 421,04</t>
+          <t>55,72; 112,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,61; 65,32</t>
+          <t>28,1; 64,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 27,05</t>
+          <t>-4,53; 26,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>80,26; 301,19</t>
+          <t>75,43; 121,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
